--- a/output/yearly_total_coral_cover_iteration_58_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_58_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.252009530029996</v>
+        <v>1.260688179735538</v>
       </c>
       <c r="C3" t="n">
-        <v>4.707388830387123</v>
+        <v>4.670131505010956</v>
       </c>
       <c r="D3" t="n">
-        <v>6.227387770343359</v>
+        <v>6.058664609891502</v>
       </c>
       <c r="E3" t="n">
-        <v>12.18678613076048</v>
+        <v>11.989484294638</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.36517430882223</v>
+        <v>1.392677324015457</v>
       </c>
       <c r="C4" t="n">
-        <v>5.380486009626234</v>
+        <v>5.223877406206705</v>
       </c>
       <c r="D4" t="n">
-        <v>6.561865380791832</v>
+        <v>6.358726112232424</v>
       </c>
       <c r="E4" t="n">
-        <v>13.3075256992403</v>
+        <v>12.97528084245459</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.520328714071852</v>
+        <v>1.571834187135504</v>
       </c>
       <c r="C5" t="n">
-        <v>6.270819722108476</v>
+        <v>5.931365606774619</v>
       </c>
       <c r="D5" t="n">
-        <v>6.943238907215932</v>
+        <v>6.72258295578571</v>
       </c>
       <c r="E5" t="n">
-        <v>14.73438734339626</v>
+        <v>14.22578274969583</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.687440792302948</v>
+        <v>1.775897455634742</v>
       </c>
       <c r="C6" t="n">
-        <v>7.343636892937476</v>
+        <v>6.842972149483011</v>
       </c>
       <c r="D6" t="n">
-        <v>7.334679577896972</v>
+        <v>7.094880636821696</v>
       </c>
       <c r="E6" t="n">
-        <v>16.3657572631374</v>
+        <v>15.71375024193945</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.873699057668536</v>
+        <v>2.002197628930471</v>
       </c>
       <c r="C7" t="n">
-        <v>8.606249804649888</v>
+        <v>7.915407290034974</v>
       </c>
       <c r="D7" t="n">
-        <v>7.815082888000666</v>
+        <v>7.48890623549273</v>
       </c>
       <c r="E7" t="n">
-        <v>18.29503175031909</v>
+        <v>17.40651115445818</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.095324977851833</v>
+        <v>1.218725413640043</v>
       </c>
       <c r="C8" t="n">
-        <v>6.287718000412551</v>
+        <v>5.56649395296137</v>
       </c>
       <c r="D8" t="n">
-        <v>6.180968718830242</v>
+        <v>5.683750722074775</v>
       </c>
       <c r="E8" t="n">
-        <v>13.56401169709463</v>
+        <v>12.46897008867619</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.333385226899075</v>
+        <v>1.529967232455927</v>
       </c>
       <c r="C9" t="n">
-        <v>7.946674967163123</v>
+        <v>6.888965556269645</v>
       </c>
       <c r="D9" t="n">
-        <v>6.762070821662256</v>
+        <v>6.183949139375549</v>
       </c>
       <c r="E9" t="n">
-        <v>16.04213101572445</v>
+        <v>14.60288192810112</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.568563288688281</v>
+        <v>1.847579502633904</v>
       </c>
       <c r="C10" t="n">
-        <v>9.797181212587297</v>
+        <v>8.357688463221615</v>
       </c>
       <c r="D10" t="n">
-        <v>7.380934862563733</v>
+        <v>6.674969301211846</v>
       </c>
       <c r="E10" t="n">
-        <v>18.74667936383931</v>
+        <v>16.88023726706736</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.791832401946757</v>
+        <v>2.170147928510239</v>
       </c>
       <c r="C11" t="n">
-        <v>11.7720069160375</v>
+        <v>9.923335124454605</v>
       </c>
       <c r="D11" t="n">
-        <v>7.905263713585026</v>
+        <v>7.135543109756373</v>
       </c>
       <c r="E11" t="n">
-        <v>21.46910303156928</v>
+        <v>19.22902616272122</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.995321309586636</v>
+        <v>2.476443212385629</v>
       </c>
       <c r="C12" t="n">
-        <v>13.81983384035408</v>
+        <v>11.58809182873449</v>
       </c>
       <c r="D12" t="n">
-        <v>8.449671579697561</v>
+        <v>7.607540758445944</v>
       </c>
       <c r="E12" t="n">
-        <v>24.26482672963828</v>
+        <v>21.67207579956607</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.169681983777247</v>
+        <v>2.776670286675406</v>
       </c>
       <c r="C13" t="n">
-        <v>15.81179924055755</v>
+        <v>13.32705548451516</v>
       </c>
       <c r="D13" t="n">
-        <v>8.933780075740737</v>
+        <v>8.056272134354272</v>
       </c>
       <c r="E13" t="n">
-        <v>26.91526130007554</v>
+        <v>24.15999790554484</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.243246022749991</v>
+        <v>1.596459211783908</v>
       </c>
       <c r="C14" t="n">
-        <v>10.89484697310855</v>
+        <v>9.36845509497674</v>
       </c>
       <c r="D14" t="n">
-        <v>6.736418952322169</v>
+        <v>6.101630704233224</v>
       </c>
       <c r="E14" t="n">
-        <v>18.87451194818071</v>
+        <v>17.06654501099387</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.218456893217759</v>
+        <v>1.622367533698982</v>
       </c>
       <c r="C15" t="n">
-        <v>11.89838947638964</v>
+        <v>10.18265773601679</v>
       </c>
       <c r="D15" t="n">
-        <v>6.758115576586024</v>
+        <v>6.090330788157343</v>
       </c>
       <c r="E15" t="n">
-        <v>19.87496194619343</v>
+        <v>17.89535605787312</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.359799110198172</v>
+        <v>1.872497213786984</v>
       </c>
       <c r="C16" t="n">
-        <v>14.01008951831636</v>
+        <v>12.06697519216291</v>
       </c>
       <c r="D16" t="n">
-        <v>7.296535470026101</v>
+        <v>6.513846930292376</v>
       </c>
       <c r="E16" t="n">
-        <v>22.66642409854064</v>
+        <v>20.45331933624227</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.057734976555514</v>
+        <v>1.494809054486194</v>
       </c>
       <c r="C17" t="n">
-        <v>12.81006984698436</v>
+        <v>11.12949449190058</v>
       </c>
       <c r="D17" t="n">
-        <v>6.788598842802887</v>
+        <v>6.018241054234499</v>
       </c>
       <c r="E17" t="n">
-        <v>20.65640366634276</v>
+        <v>18.64254460062128</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.16341029944064</v>
+        <v>1.695056133721416</v>
       </c>
       <c r="C18" t="n">
-        <v>14.81313950543617</v>
+        <v>13.02019330812431</v>
       </c>
       <c r="D18" t="n">
-        <v>7.20313199344406</v>
+        <v>6.3845114877349</v>
       </c>
       <c r="E18" t="n">
-        <v>23.17968179832087</v>
+        <v>21.09976092958062</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.13031558433048</v>
+        <v>1.687535946306885</v>
       </c>
       <c r="C19" t="n">
-        <v>15.69046852385929</v>
+        <v>13.92663114597834</v>
       </c>
       <c r="D19" t="n">
-        <v>7.274033812644765</v>
+        <v>6.436691378215618</v>
       </c>
       <c r="E19" t="n">
-        <v>24.09481792083453</v>
+        <v>22.05085847050085</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.217907114503381</v>
+        <v>1.867441213110113</v>
       </c>
       <c r="C20" t="n">
-        <v>17.78450692458661</v>
+        <v>16.03295121048578</v>
       </c>
       <c r="D20" t="n">
-        <v>7.692611763827435</v>
+        <v>6.780469971811724</v>
       </c>
       <c r="E20" t="n">
-        <v>26.69502580291742</v>
+        <v>24.68086239540762</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7060140440320513</v>
+        <v>1.103101537968759</v>
       </c>
       <c r="C21" t="n">
-        <v>12.80400264617211</v>
+        <v>11.7948838159309</v>
       </c>
       <c r="D21" t="n">
-        <v>6.420659438205267</v>
+        <v>5.61852247645041</v>
       </c>
       <c r="E21" t="n">
-        <v>19.93067612840943</v>
+        <v>18.51650783035007</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_58_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_58_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.260688179735538</v>
+        <v>1.257261880247716</v>
       </c>
       <c r="C3" t="n">
-        <v>4.670131505010956</v>
+        <v>4.599102058608699</v>
       </c>
       <c r="D3" t="n">
-        <v>6.058664609891502</v>
+        <v>6.060588835391826</v>
       </c>
       <c r="E3" t="n">
-        <v>11.989484294638</v>
+        <v>11.91695277424824</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.392677324015457</v>
+        <v>1.380015426764813</v>
       </c>
       <c r="C4" t="n">
-        <v>5.223877406206705</v>
+        <v>5.048288368103765</v>
       </c>
       <c r="D4" t="n">
-        <v>6.358726112232424</v>
+        <v>6.267582121912642</v>
       </c>
       <c r="E4" t="n">
-        <v>12.97528084245459</v>
+        <v>12.69588591678122</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.571834187135504</v>
+        <v>1.553317227693611</v>
       </c>
       <c r="C5" t="n">
-        <v>5.931365606774619</v>
+        <v>5.622118731995936</v>
       </c>
       <c r="D5" t="n">
-        <v>6.72258295578571</v>
+        <v>6.545921854634612</v>
       </c>
       <c r="E5" t="n">
-        <v>14.22578274969583</v>
+        <v>13.72135781432416</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.775897455634742</v>
+        <v>1.749749023201764</v>
       </c>
       <c r="C6" t="n">
-        <v>6.842972149483011</v>
+        <v>6.312956109806803</v>
       </c>
       <c r="D6" t="n">
-        <v>7.094880636821696</v>
+        <v>6.852950358783884</v>
       </c>
       <c r="E6" t="n">
-        <v>15.71375024193945</v>
+        <v>14.91565549179245</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.002197628930471</v>
+        <v>1.989741971407715</v>
       </c>
       <c r="C7" t="n">
-        <v>7.915407290034974</v>
+        <v>7.105800616057949</v>
       </c>
       <c r="D7" t="n">
-        <v>7.48890623549273</v>
+        <v>7.25285172869292</v>
       </c>
       <c r="E7" t="n">
-        <v>17.40651115445818</v>
+        <v>16.34839431615858</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.218725413640043</v>
+        <v>1.242962722989955</v>
       </c>
       <c r="C8" t="n">
-        <v>5.56649395296137</v>
+        <v>4.780167482875182</v>
       </c>
       <c r="D8" t="n">
-        <v>5.683750722074775</v>
+        <v>5.602597129623913</v>
       </c>
       <c r="E8" t="n">
-        <v>12.46897008867619</v>
+        <v>11.62572733548905</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.529967232455927</v>
+        <v>1.583179280435103</v>
       </c>
       <c r="C9" t="n">
-        <v>6.888965556269645</v>
+        <v>5.848661282753241</v>
       </c>
       <c r="D9" t="n">
-        <v>6.183949139375549</v>
+        <v>6.238794628881623</v>
       </c>
       <c r="E9" t="n">
-        <v>14.60288192810112</v>
+        <v>13.67063519206997</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.847579502633904</v>
+        <v>1.941365223297077</v>
       </c>
       <c r="C10" t="n">
-        <v>8.357688463221615</v>
+        <v>7.141597175960666</v>
       </c>
       <c r="D10" t="n">
-        <v>6.674969301211846</v>
+        <v>6.82497100330241</v>
       </c>
       <c r="E10" t="n">
-        <v>16.88023726706736</v>
+        <v>15.90793340256015</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.170147928510239</v>
+        <v>2.310083508081182</v>
       </c>
       <c r="C11" t="n">
-        <v>9.923335124454605</v>
+        <v>8.573049723246786</v>
       </c>
       <c r="D11" t="n">
-        <v>7.135543109756373</v>
+        <v>7.367489524798623</v>
       </c>
       <c r="E11" t="n">
-        <v>19.22902616272122</v>
+        <v>18.25062275612659</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.476443212385629</v>
+        <v>2.683446827545329</v>
       </c>
       <c r="C12" t="n">
-        <v>11.58809182873449</v>
+        <v>10.10615441015351</v>
       </c>
       <c r="D12" t="n">
-        <v>7.607540758445944</v>
+        <v>7.907421221648609</v>
       </c>
       <c r="E12" t="n">
-        <v>21.67207579956607</v>
+        <v>20.69702245934745</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.776670286675406</v>
+        <v>3.058847635449763</v>
       </c>
       <c r="C13" t="n">
-        <v>13.32705548451516</v>
+        <v>11.700378042598</v>
       </c>
       <c r="D13" t="n">
-        <v>8.056272134354272</v>
+        <v>8.507325255176314</v>
       </c>
       <c r="E13" t="n">
-        <v>24.15999790554484</v>
+        <v>23.26655093322408</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.596459211783908</v>
+        <v>1.761726620316816</v>
       </c>
       <c r="C14" t="n">
-        <v>9.36845509497674</v>
+        <v>8.199036499586109</v>
       </c>
       <c r="D14" t="n">
-        <v>6.101630704233224</v>
+        <v>6.497009957164542</v>
       </c>
       <c r="E14" t="n">
-        <v>17.06654501099387</v>
+        <v>16.45777307706746</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.622367533698982</v>
+        <v>1.824155956829871</v>
       </c>
       <c r="C15" t="n">
-        <v>10.18265773601679</v>
+        <v>8.930418904295898</v>
       </c>
       <c r="D15" t="n">
-        <v>6.090330788157343</v>
+        <v>6.573772810159601</v>
       </c>
       <c r="E15" t="n">
-        <v>17.89535605787312</v>
+        <v>17.32834767128537</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.872497213786984</v>
+        <v>2.129459857896544</v>
       </c>
       <c r="C16" t="n">
-        <v>12.06697519216291</v>
+        <v>10.60816682599144</v>
       </c>
       <c r="D16" t="n">
-        <v>6.513846930292376</v>
+        <v>7.086853795353068</v>
       </c>
       <c r="E16" t="n">
-        <v>20.45331933624227</v>
+        <v>19.82448047924106</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.494809054486194</v>
+        <v>1.717439981378243</v>
       </c>
       <c r="C17" t="n">
-        <v>11.12949449190058</v>
+        <v>9.872121119686483</v>
       </c>
       <c r="D17" t="n">
-        <v>6.018241054234499</v>
+        <v>6.609901125675882</v>
       </c>
       <c r="E17" t="n">
-        <v>18.64254460062128</v>
+        <v>18.19946222674061</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.695056133721416</v>
+        <v>1.958419772862665</v>
       </c>
       <c r="C18" t="n">
-        <v>13.02019330812431</v>
+        <v>11.53366038678491</v>
       </c>
       <c r="D18" t="n">
-        <v>6.3845114877349</v>
+        <v>7.150853928192918</v>
       </c>
       <c r="E18" t="n">
-        <v>21.09976092958062</v>
+        <v>20.64293408784049</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.687535946306885</v>
+        <v>1.963515043447706</v>
       </c>
       <c r="C19" t="n">
-        <v>13.92663114597834</v>
+        <v>12.35251651194309</v>
       </c>
       <c r="D19" t="n">
-        <v>6.436691378215618</v>
+        <v>7.290095205086242</v>
       </c>
       <c r="E19" t="n">
-        <v>22.05085847050085</v>
+        <v>21.60612676047704</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.867441213110113</v>
+        <v>2.182042264936004</v>
       </c>
       <c r="C20" t="n">
-        <v>16.03295121048578</v>
+        <v>14.22023261441039</v>
       </c>
       <c r="D20" t="n">
-        <v>6.780469971811724</v>
+        <v>7.737536538773769</v>
       </c>
       <c r="E20" t="n">
-        <v>24.68086239540762</v>
+        <v>24.13981141812016</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.103101537968759</v>
+        <v>1.293491870253343</v>
       </c>
       <c r="C21" t="n">
-        <v>11.7948838159309</v>
+        <v>10.45151916230182</v>
       </c>
       <c r="D21" t="n">
-        <v>5.61852247645041</v>
+        <v>6.488350942413086</v>
       </c>
       <c r="E21" t="n">
-        <v>18.51650783035007</v>
+        <v>18.23336197496825</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_58_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_58_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.257261880247716</v>
+        <v>2.623455189602983</v>
       </c>
       <c r="C3" t="n">
-        <v>4.599102058608699</v>
+        <v>7.728000937922038</v>
       </c>
       <c r="D3" t="n">
-        <v>6.060588835391826</v>
+        <v>8.181784997479914</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91695277424824</v>
+        <v>18.53324112500493</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.380015426764813</v>
+        <v>1.155807852089743</v>
       </c>
       <c r="C4" t="n">
-        <v>5.048288368103765</v>
+        <v>4.533083118019001</v>
       </c>
       <c r="D4" t="n">
-        <v>6.267582121912642</v>
+        <v>5.756801392585572</v>
       </c>
       <c r="E4" t="n">
-        <v>12.69588591678122</v>
+        <v>11.44569236269432</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.553317227693611</v>
+        <v>1.329643434249692</v>
       </c>
       <c r="C5" t="n">
-        <v>5.622118731995936</v>
+        <v>5.237509000523757</v>
       </c>
       <c r="D5" t="n">
-        <v>6.545921854634612</v>
+        <v>6.081141477267647</v>
       </c>
       <c r="E5" t="n">
-        <v>13.72135781432416</v>
+        <v>12.6482939120411</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.749749023201764</v>
+        <v>1.515468551518286</v>
       </c>
       <c r="C6" t="n">
-        <v>6.312956109806803</v>
+        <v>6.167018408348119</v>
       </c>
       <c r="D6" t="n">
-        <v>6.852950358783884</v>
+        <v>6.394262466240034</v>
       </c>
       <c r="E6" t="n">
-        <v>14.91565549179245</v>
+        <v>14.07674942610644</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.989741971407715</v>
+        <v>1.705661422158582</v>
       </c>
       <c r="C7" t="n">
-        <v>7.105800616057949</v>
+        <v>7.33744399332188</v>
       </c>
       <c r="D7" t="n">
-        <v>7.25285172869292</v>
+        <v>6.731146441780422</v>
       </c>
       <c r="E7" t="n">
-        <v>16.34839431615858</v>
+        <v>15.77425185726088</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.242962722989955</v>
+        <v>1.893872821879087</v>
       </c>
       <c r="C8" t="n">
-        <v>4.780167482875182</v>
+        <v>8.748828863244389</v>
       </c>
       <c r="D8" t="n">
-        <v>5.602597129623913</v>
+        <v>7.036188990848813</v>
       </c>
       <c r="E8" t="n">
-        <v>11.62572733548905</v>
+        <v>17.67889067597229</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.583179280435103</v>
+        <v>2.08061929154057</v>
       </c>
       <c r="C9" t="n">
-        <v>5.848661282753241</v>
+        <v>10.31540432429731</v>
       </c>
       <c r="D9" t="n">
-        <v>6.238794628881623</v>
+        <v>7.417682569561545</v>
       </c>
       <c r="E9" t="n">
-        <v>13.67063519206997</v>
+        <v>19.81370618539942</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.941365223297077</v>
+        <v>1.257294832397763</v>
       </c>
       <c r="C10" t="n">
-        <v>7.141597175960666</v>
+        <v>7.574124633401887</v>
       </c>
       <c r="D10" t="n">
-        <v>6.82497100330241</v>
+        <v>5.817748538073216</v>
       </c>
       <c r="E10" t="n">
-        <v>15.90793340256015</v>
+        <v>14.64916800387287</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.310083508081182</v>
+        <v>1.21651303276335</v>
       </c>
       <c r="C11" t="n">
-        <v>8.573049723246786</v>
+        <v>8.332043678557469</v>
       </c>
       <c r="D11" t="n">
-        <v>7.367489524798623</v>
+        <v>5.632797088070159</v>
       </c>
       <c r="E11" t="n">
-        <v>18.25062275612659</v>
+        <v>15.18135379939098</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.683446827545329</v>
+        <v>1.34356100316993</v>
       </c>
       <c r="C12" t="n">
-        <v>10.10615441015351</v>
+        <v>10.02685437535282</v>
       </c>
       <c r="D12" t="n">
-        <v>7.907421221648609</v>
+        <v>6.03869085891396</v>
       </c>
       <c r="E12" t="n">
-        <v>20.69702245934745</v>
+        <v>17.40910623743671</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.058847635449763</v>
+        <v>1.071410722075672</v>
       </c>
       <c r="C13" t="n">
-        <v>11.700378042598</v>
+        <v>9.63583408222836</v>
       </c>
       <c r="D13" t="n">
-        <v>8.507325255176314</v>
+        <v>5.488902327058704</v>
       </c>
       <c r="E13" t="n">
-        <v>23.26655093322408</v>
+        <v>16.19614713136274</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.761726620316816</v>
+        <v>1.170910851901086</v>
       </c>
       <c r="C14" t="n">
-        <v>8.199036499586109</v>
+        <v>11.35274391984631</v>
       </c>
       <c r="D14" t="n">
-        <v>6.497009957164542</v>
+        <v>5.787500891305371</v>
       </c>
       <c r="E14" t="n">
-        <v>16.45777307706746</v>
+        <v>18.31115566305277</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.824155956829871</v>
+        <v>1.139593100135613</v>
       </c>
       <c r="C15" t="n">
-        <v>8.930418904295898</v>
+        <v>12.30733648259365</v>
       </c>
       <c r="D15" t="n">
-        <v>6.573772810159601</v>
+        <v>5.81013017588826</v>
       </c>
       <c r="E15" t="n">
-        <v>17.32834767128537</v>
+        <v>19.25705975861753</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.129459857896544</v>
+        <v>1.245631669671311</v>
       </c>
       <c r="C16" t="n">
-        <v>10.60816682599144</v>
+        <v>14.25445633938044</v>
       </c>
       <c r="D16" t="n">
-        <v>7.086853795353068</v>
+        <v>6.167339078078463</v>
       </c>
       <c r="E16" t="n">
-        <v>19.82448047924106</v>
+        <v>21.66742708713021</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.717439981378243</v>
+        <v>0.7361733335065133</v>
       </c>
       <c r="C17" t="n">
-        <v>9.872121119686483</v>
+        <v>10.51264277436823</v>
       </c>
       <c r="D17" t="n">
-        <v>6.609901125675882</v>
+        <v>5.10610907969583</v>
       </c>
       <c r="E17" t="n">
-        <v>18.19946222674061</v>
+        <v>16.35492518757057</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.958419772862665</v>
+        <v>0.5892744245200631</v>
       </c>
       <c r="C18" t="n">
-        <v>11.53366038678491</v>
+        <v>9.358961594676675</v>
       </c>
       <c r="D18" t="n">
-        <v>7.150853928192918</v>
+        <v>4.627330359288747</v>
       </c>
       <c r="E18" t="n">
-        <v>20.64293408784049</v>
+        <v>14.57556637848548</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.963515043447706</v>
+        <v>0.6876553619626359</v>
       </c>
       <c r="C19" t="n">
-        <v>12.35251651194309</v>
+        <v>11.48723353785108</v>
       </c>
       <c r="D19" t="n">
-        <v>7.290095205086242</v>
+        <v>5.085590552677073</v>
       </c>
       <c r="E19" t="n">
-        <v>21.60612676047704</v>
+        <v>17.26047945249079</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.182042264936004</v>
+        <v>0.7790069858428016</v>
       </c>
       <c r="C20" t="n">
-        <v>14.22023261441039</v>
+        <v>13.76748002564289</v>
       </c>
       <c r="D20" t="n">
-        <v>7.737536538773769</v>
+        <v>5.520534238089537</v>
       </c>
       <c r="E20" t="n">
-        <v>24.13981141812016</v>
+        <v>20.06702124957523</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.293491870253343</v>
+        <v>0.8597066471318895</v>
       </c>
       <c r="C21" t="n">
-        <v>10.45151916230182</v>
+        <v>16.03390350575891</v>
       </c>
       <c r="D21" t="n">
-        <v>6.488350942413086</v>
+        <v>5.900215345229949</v>
       </c>
       <c r="E21" t="n">
-        <v>18.23336197496825</v>
+        <v>22.79382549812075</v>
       </c>
     </row>
   </sheetData>
